--- a/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,22 +838,22 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CELLINI LUCA.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,22 +838,22 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
